--- a/code/Hist2Pheno_pkg/dataset/PanCancerCellType.xlsx
+++ b/code/Hist2Pheno_pkg/dataset/PanCancerCellType.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="celltype" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="celltype_v1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="celltype_fine" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lung" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRCA" sheetId="6" state="visible" r:id="rId6"/>
@@ -20,8 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GBM_unique_L2" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'celltype'!$A$1:$H$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'celltype_v1'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'celltype'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'celltype_fine'!$A$1:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'summary'!$A$1:$Q$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Lung'!$A$1:$Q$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRCA'!$A$1:$M$21</definedName>
@@ -88,22 +88,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -246,17 +246,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_celltype" displayName="T_celltype" ref="A1:H69" headerRowCount="1">
-  <autoFilter ref="A1:H69"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_celltype" displayName="T_celltype" ref="A1:J22" headerRowCount="1">
+  <autoFilter ref="A1:J22"/>
+  <tableColumns count="10">
     <tableColumn id="1" name="L1"/>
     <tableColumn id="2" name="L12"/>
     <tableColumn id="3" name="L2"/>
     <tableColumn id="4" name="L2_aliases"/>
     <tableColumn id="5" name="present_in"/>
-    <tableColumn id="6" name="reserved_for"/>
-    <tableColumn id="7" name="trainable"/>
-    <tableColumn id="8" name="notes"/>
+    <tableColumn id="6" name="l2_scope"/>
+    <tableColumn id="7" name="reserved_for"/>
+    <tableColumn id="8" name="trainable"/>
+    <tableColumn id="9" name="index_role"/>
+    <tableColumn id="10" name="notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -282,9 +284,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_celltype_v1" displayName="T_celltype_v1" ref="A1:I22" headerRowCount="1">
-  <autoFilter ref="A1:I22"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_celltype_fine" displayName="T_celltype_fine" ref="A1:H69" headerRowCount="1">
+  <autoFilter ref="A1:H69"/>
+  <tableColumns count="8">
     <tableColumn id="1" name="L1"/>
     <tableColumn id="2" name="L12"/>
     <tableColumn id="3" name="L2"/>
@@ -292,8 +294,7 @@
     <tableColumn id="5" name="present_in"/>
     <tableColumn id="6" name="reserved_for"/>
     <tableColumn id="7" name="trainable"/>
-    <tableColumn id="8" name="index_role"/>
-    <tableColumn id="9" name="notes"/>
+    <tableColumn id="8" name="notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -756,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -773,7 +774,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One workbook: sheet celltype = v0 inventory (5/11/59); sheet celltype_v1 = HE-realistic training heads (5/8/20). CODEX ESCC omitted.</t>
+          <t>One workbook: sheet celltype = HE-realistic training heads (5/8/20 = 17 core + 3 lung); sheet celltype_fine = v0 inventory (5/11/59). CODEX ESCC omitted.</t>
         </is>
       </c>
     </row>
@@ -821,19 +822,19 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>v0 synonym inventory: 5 L1 / 11 L12 / 59 trainable L2. Too fine for a 16 px H&amp;E patch.</t>
+          <t>HE-realistic training ontology: 5 L1 / 8 L12 / 20 L2 = 17-class 5-cancer union (core) + 3 coarse lung extras. Use this for pan-cancer Hist2Pheno.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>celltype_v1 sheet</t>
+          <t>celltype_fine sheet</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>HE-realistic training ontology: 5 L1 / 8 L12 / 20 L2. Use this for pan-cancer Hist2Pheno.</t>
+          <t>v0 synonym inventory: 5 L1 / 11 L12 / 59 trainable L2. Too fine for a 16 px H&amp;E patch.</t>
         </is>
       </c>
     </row>
@@ -864,70 +865,94 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>L2 v1</t>
+          <t>L2 v1 core</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Tumor, DCIS, Alveolar, Epithelial, Injury_epithelial, Myoepithelial, CD4_T, CD8_T, T_cell, B_cell, Plasma, DC, Macrophage, Macrophage_activated, Neutrophil, Fibroblast, Myofibroblast, Stromal, Endothelial, Neural.</t>
+          <t>5-cancer union (17): Tumor, DCIS, Epithelial, Myoepithelial, CD4_T, CD8_T, T_cell, B_cell, Plasma, DC, Macrophage, Macrophage_activated, Neutrophil, Fibroblast, Stromal, Endothelial, Neural.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Dataset sheets</t>
+          <t>L2 v1 lung extras</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Original multi-level table + v0 columns L1/L12/L2 + v1 columns L1_v1/L12_v1/L2_v1.</t>
+          <t>Coarse only: Alveolar (AT1+AT2+prolif AT2), Injury_epithelial (KRT5-/KRT17++RASC+transitional AT2), Myofibroblast (myofibroblast+activated/inflammatory/prolif FBs). Do not add AT1 vs AT2 or FB subtypes.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>GBM L12</t>
+          <t>Lung merge</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Native L12 is spatial niche SN1–SN9. Unified L12 ignores SN and uses cell_type / subcluster biology.</t>
+          <t>Airway / mesothelial → Epithelial; homeostatic FBs → Fibroblast; T/B/DC/mac/neutrophil/endothelial synonyms → matching core class. See l2_scope on celltype.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>How to add CRC / Prostate</t>
+          <t>Dataset sheets</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>New sheet with native labels. Map onto celltype_v1 L2 (Tumor / Epithelial / Neural / Stromal). Do not add new v1 L2 rows.</t>
+          <t>Original multi-level table + v0 columns L1/L12/L2 + v1 columns L1_v1/L12_v1/L2_v1.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Head names</t>
+          <t>GBM L12</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Hist2Pheno train heads: L2=fine=final_CT, L12=intermediate=final_sublineage, L1=coarse=final_lineage.</t>
+          <t>Native L12 is spatial niche SN1–SN9. Unified L12 ignores SN and uses cell_type / subcluster biology.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>How to add CRC / Prostate</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>New sheet with native labels. Map onto celltype L2 (Tumor / Epithelial / Neural / Stromal). Do not add new celltype L2 rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Head names</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Hist2Pheno train heads: L2=fine=final_CT, L12=intermediate=final_sublineage, L1=coarse=final_lineage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>Counts</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>GT_cells_on_HE from Hist2Pheno_Datasets.xlsx (2026-09-09 snapshot). Lung GT cells = Complete_Cases only.</t>
         </is>
@@ -4888,7 +4913,7 @@
       <c r="I50" s="4" t="n">
         <v/>
       </c>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -4967,7 +4992,7 @@
       <c r="I51" s="4" t="n">
         <v/>
       </c>
-      <c r="J51" s="9" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5046,7 +5071,7 @@
       <c r="I52" s="4" t="n">
         <v/>
       </c>
-      <c r="J52" s="9" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5125,7 +5150,7 @@
       <c r="I53" s="4" t="n">
         <v/>
       </c>
-      <c r="J53" s="9" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5204,7 +5229,7 @@
       <c r="I54" s="4" t="n">
         <v/>
       </c>
-      <c r="J54" s="9" t="inlineStr">
+      <c r="J54" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5283,7 +5308,7 @@
       <c r="I55" s="4" t="n">
         <v/>
       </c>
-      <c r="J55" s="9" t="inlineStr">
+      <c r="J55" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5362,7 +5387,7 @@
       <c r="I56" s="4" t="n">
         <v/>
       </c>
-      <c r="J56" s="9" t="inlineStr">
+      <c r="J56" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5441,7 +5466,7 @@
       <c r="I57" s="4" t="n">
         <v/>
       </c>
-      <c r="J57" s="9" t="inlineStr">
+      <c r="J57" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5520,7 +5545,7 @@
       <c r="I58" s="4" t="n">
         <v/>
       </c>
-      <c r="J58" s="9" t="inlineStr">
+      <c r="J58" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5599,7 +5624,7 @@
       <c r="I59" s="4" t="n">
         <v/>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="J59" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5678,7 +5703,7 @@
       <c r="I60" s="4" t="n">
         <v/>
       </c>
-      <c r="J60" s="9" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5757,7 +5782,7 @@
       <c r="I61" s="4" t="n">
         <v/>
       </c>
-      <c r="J61" s="9" t="inlineStr">
+      <c r="J61" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5836,7 +5861,7 @@
       <c r="I62" s="4" t="n">
         <v/>
       </c>
-      <c r="J62" s="9" t="inlineStr">
+      <c r="J62" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5915,7 +5940,7 @@
       <c r="I63" s="4" t="n">
         <v/>
       </c>
-      <c r="J63" s="9" t="inlineStr">
+      <c r="J63" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -5994,7 +6019,7 @@
       <c r="I64" s="4" t="n">
         <v/>
       </c>
-      <c r="J64" s="9" t="inlineStr">
+      <c r="J64" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6073,7 +6098,7 @@
       <c r="I65" s="4" t="n">
         <v/>
       </c>
-      <c r="J65" s="9" t="inlineStr">
+      <c r="J65" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6152,7 +6177,7 @@
       <c r="I66" s="4" t="n">
         <v/>
       </c>
-      <c r="J66" s="9" t="inlineStr">
+      <c r="J66" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6231,7 +6256,7 @@
       <c r="I67" s="4" t="n">
         <v/>
       </c>
-      <c r="J67" s="9" t="inlineStr">
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6310,7 +6335,7 @@
       <c r="I68" s="4" t="n">
         <v/>
       </c>
-      <c r="J68" s="9" t="inlineStr">
+      <c r="J68" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6389,7 +6414,7 @@
       <c r="I69" s="4" t="n">
         <v/>
       </c>
-      <c r="J69" s="9" t="inlineStr">
+      <c r="J69" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6468,7 +6493,7 @@
       <c r="I70" s="4" t="n">
         <v/>
       </c>
-      <c r="J70" s="9" t="inlineStr">
+      <c r="J70" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6547,7 +6572,7 @@
       <c r="I71" s="4" t="n">
         <v/>
       </c>
-      <c r="J71" s="9" t="inlineStr">
+      <c r="J71" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6626,7 +6651,7 @@
       <c r="I72" s="4" t="n">
         <v/>
       </c>
-      <c r="J72" s="9" t="inlineStr">
+      <c r="J72" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6705,7 +6730,7 @@
       <c r="I73" s="4" t="n">
         <v/>
       </c>
-      <c r="J73" s="9" t="inlineStr">
+      <c r="J73" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6784,7 +6809,7 @@
       <c r="I74" s="4" t="n">
         <v/>
       </c>
-      <c r="J74" s="9" t="inlineStr">
+      <c r="J74" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6863,7 +6888,7 @@
       <c r="I75" s="4" t="n">
         <v/>
       </c>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J75" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -6942,7 +6967,7 @@
       <c r="I76" s="4" t="n">
         <v/>
       </c>
-      <c r="J76" s="9" t="inlineStr">
+      <c r="J76" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7023,7 +7048,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr">
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7104,7 +7129,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="J78" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7185,7 +7210,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7266,7 +7291,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr">
+      <c r="J80" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7347,7 +7372,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
+      <c r="J81" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7428,7 +7453,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
+      <c r="J82" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7509,7 +7534,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J83" s="9" t="inlineStr">
+      <c r="J83" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7588,7 +7613,7 @@
       <c r="I84" s="4" t="n">
         <v/>
       </c>
-      <c r="J84" s="9" t="inlineStr">
+      <c r="J84" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7667,7 +7692,7 @@
       <c r="I85" s="4" t="n">
         <v/>
       </c>
-      <c r="J85" s="9" t="inlineStr">
+      <c r="J85" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7746,7 +7771,7 @@
       <c r="I86" s="4" t="n">
         <v/>
       </c>
-      <c r="J86" s="9" t="inlineStr">
+      <c r="J86" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7825,7 +7850,7 @@
       <c r="I87" s="4" t="n">
         <v/>
       </c>
-      <c r="J87" s="9" t="inlineStr">
+      <c r="J87" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7904,7 +7929,7 @@
       <c r="I88" s="4" t="n">
         <v/>
       </c>
-      <c r="J88" s="9" t="inlineStr">
+      <c r="J88" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -7983,7 +8008,7 @@
       <c r="I89" s="4" t="n">
         <v/>
       </c>
-      <c r="J89" s="9" t="inlineStr">
+      <c r="J89" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -8062,7 +8087,7 @@
       <c r="I90" s="4" t="n">
         <v/>
       </c>
-      <c r="J90" s="9" t="inlineStr">
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -8141,7 +8166,7 @@
       <c r="I91" s="4" t="n">
         <v/>
       </c>
-      <c r="J91" s="9" t="inlineStr">
+      <c r="J91" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -8220,7 +8245,7 @@
       <c r="I92" s="4" t="n">
         <v/>
       </c>
-      <c r="J92" s="9" t="inlineStr">
+      <c r="J92" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -9012,7 +9037,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J102" s="9" t="inlineStr">
+      <c r="J102" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -9093,7 +9118,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J103" s="9" t="inlineStr">
+      <c r="J103" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -9174,7 +9199,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J104" s="9" t="inlineStr">
+      <c r="J104" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -9255,7 +9280,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J105" s="9" t="inlineStr">
+      <c r="J105" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -9336,7 +9361,7 @@
           <t>Mac_SEPP1 maps to multiple cell_type values (Ini vs Rec)</t>
         </is>
       </c>
-      <c r="J106" s="9" t="inlineStr">
+      <c r="J106" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -9415,7 +9440,7 @@
       <c r="I107" s="4" t="n">
         <v/>
       </c>
-      <c r="J107" s="8" t="inlineStr">
+      <c r="J107" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -9494,7 +9519,7 @@
       <c r="I108" s="4" t="n">
         <v/>
       </c>
-      <c r="J108" s="8" t="inlineStr">
+      <c r="J108" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -9573,7 +9598,7 @@
       <c r="I109" s="4" t="n">
         <v/>
       </c>
-      <c r="J109" s="8" t="inlineStr">
+      <c r="J109" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -9652,7 +9677,7 @@
       <c r="I110" s="4" t="n">
         <v/>
       </c>
-      <c r="J110" s="8" t="inlineStr">
+      <c r="J110" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -9731,7 +9756,7 @@
       <c r="I111" s="4" t="n">
         <v/>
       </c>
-      <c r="J111" s="8" t="inlineStr">
+      <c r="J111" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -9810,7 +9835,7 @@
       <c r="I112" s="4" t="n">
         <v/>
       </c>
-      <c r="J112" s="8" t="inlineStr">
+      <c r="J112" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -9889,7 +9914,7 @@
       <c r="I113" s="4" t="n">
         <v/>
       </c>
-      <c r="J113" s="8" t="inlineStr">
+      <c r="J113" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -9968,7 +9993,7 @@
       <c r="I114" s="4" t="n">
         <v/>
       </c>
-      <c r="J114" s="8" t="inlineStr">
+      <c r="J114" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -10047,7 +10072,7 @@
       <c r="I115" s="4" t="n">
         <v/>
       </c>
-      <c r="J115" s="8" t="inlineStr">
+      <c r="J115" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -10126,7 +10151,7 @@
       <c r="I116" s="4" t="n">
         <v/>
       </c>
-      <c r="J116" s="10" t="inlineStr">
+      <c r="J116" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10205,7 +10230,7 @@
       <c r="I117" s="4" t="n">
         <v/>
       </c>
-      <c r="J117" s="10" t="inlineStr">
+      <c r="J117" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10284,7 +10309,7 @@
       <c r="I118" s="4" t="n">
         <v/>
       </c>
-      <c r="J118" s="10" t="inlineStr">
+      <c r="J118" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10363,7 +10388,7 @@
       <c r="I119" s="4" t="n">
         <v/>
       </c>
-      <c r="J119" s="10" t="inlineStr">
+      <c r="J119" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10442,7 +10467,7 @@
       <c r="I120" s="4" t="n">
         <v/>
       </c>
-      <c r="J120" s="10" t="inlineStr">
+      <c r="J120" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10521,7 +10546,7 @@
       <c r="I121" s="4" t="n">
         <v/>
       </c>
-      <c r="J121" s="10" t="inlineStr">
+      <c r="J121" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10600,7 +10625,7 @@
       <c r="I122" s="4" t="n">
         <v/>
       </c>
-      <c r="J122" s="10" t="inlineStr">
+      <c r="J122" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10679,7 +10704,7 @@
       <c r="I123" s="4" t="n">
         <v/>
       </c>
-      <c r="J123" s="10" t="inlineStr">
+      <c r="J123" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10758,7 +10783,7 @@
       <c r="I124" s="4" t="n">
         <v/>
       </c>
-      <c r="J124" s="10" t="inlineStr">
+      <c r="J124" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10837,7 +10862,7 @@
       <c r="I125" s="4" t="n">
         <v/>
       </c>
-      <c r="J125" s="10" t="inlineStr">
+      <c r="J125" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10916,7 +10941,7 @@
       <c r="I126" s="4" t="n">
         <v/>
       </c>
-      <c r="J126" s="10" t="inlineStr">
+      <c r="J126" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -10995,7 +11020,7 @@
       <c r="I127" s="4" t="n">
         <v/>
       </c>
-      <c r="J127" s="10" t="inlineStr">
+      <c r="J127" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -11074,7 +11099,7 @@
       <c r="I128" s="4" t="n">
         <v/>
       </c>
-      <c r="J128" s="10" t="inlineStr">
+      <c r="J128" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -11153,7 +11178,7 @@
       <c r="I129" s="4" t="n">
         <v/>
       </c>
-      <c r="J129" s="10" t="inlineStr">
+      <c r="J129" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -11232,7 +11257,7 @@
       <c r="I130" s="4" t="n">
         <v/>
       </c>
-      <c r="J130" s="10" t="inlineStr">
+      <c r="J130" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -11311,7 +11336,7 @@
       <c r="I131" s="4" t="n">
         <v/>
       </c>
-      <c r="J131" s="10" t="inlineStr">
+      <c r="J131" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -11390,7 +11415,7 @@
       <c r="I132" s="4" t="n">
         <v/>
       </c>
-      <c r="J132" s="10" t="inlineStr">
+      <c r="J132" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -11469,7 +11494,7 @@
       <c r="I133" s="4" t="n">
         <v/>
       </c>
-      <c r="J133" s="8" t="inlineStr">
+      <c r="J133" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -11548,7 +11573,7 @@
       <c r="I134" s="4" t="n">
         <v/>
       </c>
-      <c r="J134" s="8" t="inlineStr">
+      <c r="J134" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -11627,7 +11652,7 @@
       <c r="I135" s="4" t="n">
         <v/>
       </c>
-      <c r="J135" s="8" t="inlineStr">
+      <c r="J135" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -11706,7 +11731,7 @@
       <c r="I136" s="4" t="n">
         <v/>
       </c>
-      <c r="J136" s="8" t="inlineStr">
+      <c r="J136" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -11785,7 +11810,7 @@
       <c r="I137" s="4" t="n">
         <v/>
       </c>
-      <c r="J137" s="8" t="inlineStr">
+      <c r="J137" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -11864,7 +11889,7 @@
       <c r="I138" s="4" t="n">
         <v/>
       </c>
-      <c r="J138" s="8" t="inlineStr">
+      <c r="J138" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -11943,7 +11968,7 @@
       <c r="I139" s="4" t="n">
         <v/>
       </c>
-      <c r="J139" s="8" t="inlineStr">
+      <c r="J139" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -12022,7 +12047,7 @@
       <c r="I140" s="4" t="n">
         <v/>
       </c>
-      <c r="J140" s="8" t="inlineStr">
+      <c r="J140" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -12101,7 +12126,7 @@
       <c r="I141" s="4" t="n">
         <v/>
       </c>
-      <c r="J141" s="8" t="inlineStr">
+      <c r="J141" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -12235,7 +12260,7 @@
           <t>Vascular</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -12287,7 +12312,7 @@
           <t>Vascular</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -12651,7 +12676,7 @@
           <t>Lymph</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -12703,7 +12728,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -12755,7 +12780,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -12807,7 +12832,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -12859,7 +12884,7 @@
           <t>Vascular</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -12911,7 +12936,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -13015,7 +13040,7 @@
           <t>Vascular</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -13067,7 +13092,7 @@
           <t>Vascular</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -13118,6 +13143,1116 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="72" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>L2_aliases</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>present_in</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>l2_scope</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>reserved_for</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>trainable</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>index_role</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>DCIS</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>DCIS_1; DCIS_2</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>BRCA</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>in situ tumor</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>BRCA DCIS (DCIS_1 + DCIS_2). One class: the 1/2 split is BRCA-only and not needed pan-cancer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>AC-like; Epithelium (INOS+); Epithelium (INOS-); G1S; G2M; Invasive_Tumor; MES-like; NPC-like; OC-like; Prolif_Invasive_Tumor; T_Cell_&amp;_Tumor_Hybrid</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>BRCA; HCC; GBM</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CRC; Prostate; extra HCC</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>malignant compartment</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Invasive / cycling malignant parenchyma (BRCA invasive, HCC INOS±, GBM states). Reserved for CRC / Prostate tumor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Alveolar</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>AT1; AT2; Proliferating AT2</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Lung</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>lung_unique</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>FRI/ARI denominator (lung extra)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Lung-unique extra (coarse): AT1 + AT2 + proliferating AT2. FRI/ARI denominator. Not in the 5-cancer union.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Basal; Epithelial cells; Goblet; Mesothelial; Multiciliated; PNEC; Proliferating Airway; Secretory</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Lung; PDAC; GIST</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CRC (Enterocyte/Tuft/Goblet); Prostate (Luminal)</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>normal / residual / airway epithelium</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Residual / airway / mixed epithelium (PDAC, GIST, lung secretory/basal/goblet/mesothelial). CRC Enterocyte / Prostate Luminal map here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Injury_epithelial</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>KRT5-/KRT17+; RASC; Transitional AT2</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Lung</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>lung_unique</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>FRI numerator (lung extra)</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Lung-unique extra (coarse): KRT5-/KRT17+ + RASC + transitional AT2. FRI injury numerator. Not AT1 vs RASC vs KRT5 as separate heads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Myoepithelial</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Myoepi_ACTA2+; Myoepi_KRT15+</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>BRCA</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Prostate basal</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>breast architecture</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Breast myoepithelium (WSI-visible as a layer; hard on a 16 px patch).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CD4_T</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>CD4 T cells; CD4+ T-cells; CD4+_T_Cells; Helper T cells; Tregs</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>TLS T</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Helper / CD4 T (incl. Treg). Split from CD8 because nuclear size and helper vs cytotoxic cues are weakly visible on H&amp;E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CD8_T</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>CD8 T cells; CD8+ T-cells; CD8+_T_Cells; Cytotoxic T cells</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; HCC; PDAC</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>TLS T</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Cytotoxic / CD8 T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>INFg+; Lymphocyte; NK/NKT; Proliferating NK/NKT; Proliferating T-cells; T cells</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Lung; HCC; GIST; GBM</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Unspecified T / NK / GBM Lymphocyte / proliferating T / INFg+. Use when the source does not split CD4 vs CD8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>B_cell</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>B cells; B_Cells; Proliferating B cells</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>TLS B compartment (incl. proliferating B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Plasma cells</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Lung; PDAC</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>TLS-adjacent</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Clock-face plasma cells; kept because they are often H&amp;E-visible and sit in TLS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>DCs; Dendritic cells; IRF7+_DCs; LAMP3+_DCs; Langerhans cells; Migratory DCs; cDCs; pDCs</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>TLS third member. All DC / pDC / Langerhans collapsed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Macrophage</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Alveolar Macrophages; Interstitial Macrophages; Mac_SEPP1; Mac_Tmr; Mac_other; Macrophages; Macrophages_1; Macrophages_2; Monocytes; Proliferating Myeloid</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>TNI myeloid</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Generic macrophages + GIST monocytes. TNI myeloid = this + Macrophage_activated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Macrophage_activated</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Mac_SPP1; Macrophages - IFN-activated; Macrophages M2-like; Monocytes/MDMs; SPP1+ Macrophages</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Lung; HCC; GBM</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>TNI M2 / FRI profibrotic mac</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>TNI M2 / FRI profibrotic macs: M2-like, SPP1+, IFN-activated, Monocytes/MDMs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Neutrophil</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Basophils; Mast; Mast_Cells; Neutrophils</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>inflammation</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Granulocytes (neutrophil + basophil + mast). Mast granules are H&amp;E-visible but too rare to keep a head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Adventitial FBs; Alveolar FBs; Fibroblasts; Subpleural FBs</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Lung; HCC; PDAC; GIST</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>SRI / baseline stroma</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Quiescent / tissue fibroblasts (lung alveolar/adventitial/subpleural FBs; CODEX Fibroblasts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Myofibroblast</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Activated Fibrotic FBs; Inflammatory FBs; Myofibroblasts; Proliferating FBs</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Lung</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>lung_unique</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>ARI + FRI fibrotic stroma (lung extra)</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Lung-unique extra (coarse): myofibroblasts + activated/inflammatory/proliferating FBs. ARI + FRI fibrotic-stromal numerator. One class, not four FB states.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Unknown; Unlabeled; Other; Stroma Uncharacterized; LowQ</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>excluded</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>excluded</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>Dropped at train time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>CAF; Collagen_fibrils; Perivascular-Like; SMCs/Pericytes; Stromal cells; Stromal_&amp;_T_Cell_Hybrid</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; GIST; GBM</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>CRC / Prostate smooth muscle; GIST tumor</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>SRI / GIST tumor</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>CAF, collagen, GIST stromal/tumor, SMC/pericyte. GIST tumor stays here (mesenchymal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Arteriole; Capillary; Endothelial cells; Lymphatic; Lymphatic Endothelial cells; Vascular; Venous; lowQ_vas</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>TNI endothelium</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Blood + lymphatic + GBM Vascular. TNI endothelium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Neural</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Neural</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Neural</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Oligodendrocyte</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>GBM</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>core_5union</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Prostate / CRC / PDAC nerve</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>glia / reserved nerve</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Oligodendrocyte; reserved Nerve for prostate / CRC / PDAC.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13456,33 +14591,33 @@
           <t>Epithelial</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Tumor</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Tumor_T_hybrid</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>T_Cell_&amp;_Tumor_Hybrid</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>BRCA</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>BRCA red L2; dropped at match. Listed so the native name still maps.</t>
         </is>
@@ -13613,34 +14748,34 @@
       <c r="H14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Enterocyte</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>CRC</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Intestinal absorptive epithelium.</t>
         </is>
@@ -13749,34 +14884,34 @@
       <c r="H18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Luminal</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Prostate</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Prostate luminal epithelium.</t>
         </is>
@@ -14035,68 +15170,68 @@
       <c r="H27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Tuft</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>CRC</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Rare intestinal chemosensory cell.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Myoepithelial</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>Basal_myoepithelial</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Prostate; BRCA</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>Prostate basal / breast myoepithelial if not already Myoepithelial.</t>
         </is>
@@ -14137,7 +15272,7 @@
       <c r="H30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14171,7 +15306,7 @@
       <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14205,7 +15340,7 @@
       <c r="H32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14239,7 +15374,7 @@
       <c r="H33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14273,7 +15408,7 @@
       <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14307,7 +15442,7 @@
       <c r="H35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14341,7 +15476,7 @@
       <c r="H36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14375,7 +15510,7 @@
       <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14409,7 +15544,7 @@
       <c r="H38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14443,7 +15578,7 @@
       <c r="H39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14477,7 +15612,7 @@
       <c r="H40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14511,7 +15646,7 @@
       <c r="H41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14545,7 +15680,7 @@
       <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14579,7 +15714,7 @@
       <c r="H43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14613,7 +15748,7 @@
       <c r="H44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14647,7 +15782,7 @@
       <c r="H45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14681,7 +15816,7 @@
       <c r="H46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14715,7 +15850,7 @@
       <c r="H47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14749,7 +15884,7 @@
       <c r="H48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14783,7 +15918,7 @@
       <c r="H49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14817,7 +15952,7 @@
       <c r="H50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14847,7 +15982,7 @@
       <c r="H51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14881,7 +16016,7 @@
       <c r="H52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -14915,7 +16050,7 @@
       <c r="H53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -14945,7 +16080,7 @@
       <c r="H54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -14979,7 +16114,7 @@
       <c r="H55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -15013,7 +16148,7 @@
       <c r="H56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -15047,79 +16182,79 @@
       <c r="H57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>Unknown; Unlabeled; Other; Stroma Uncharacterized; LowQ</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr"/>
+      <c r="G58" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H58" s="9" t="inlineStr">
         <is>
           <t>Dropped at train time. Kept only so new datasets can park Unknown / Other.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>Smooth_muscle</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr"/>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="D59" s="10" t="inlineStr"/>
+      <c r="E59" s="10" t="inlineStr"/>
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>CRC; Prostate; GIST</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Muscularis / vascular smooth muscle if split from SMC_Pericyte.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -15157,45 +16292,45 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>Stromal_T_hybrid</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>Stromal_&amp;_T_Cell_Hybrid</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>BRCA</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr"/>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr"/>
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="H61" s="9" t="inlineStr">
         <is>
           <t>BRCA red L2; dropped at match.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -15229,7 +16364,7 @@
       <c r="H62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -15259,7 +16394,7 @@
       <c r="H63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -15289,7 +16424,7 @@
       <c r="H64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -15323,7 +16458,7 @@
       <c r="H65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -15357,7 +16492,7 @@
       <c r="H66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -15387,34 +16522,34 @@
       <c r="H67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>Neural</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>Neural</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>Nerve</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr"/>
+      <c r="E68" s="10" t="inlineStr"/>
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>Prostate; CRC; PDAC</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Nerve fascicles / Schwann / enteric glia on H&amp;E.</t>
         </is>
@@ -15452,1005 +16587,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H69"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="72" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>L12</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>L2_aliases</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>present_in</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>reserved_for</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>trainable</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>index_role</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Tumor</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>DCIS</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>DCIS_1; DCIS_2</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>BRCA</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>in situ tumor</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>BRCA DCIS (DCIS_1 + DCIS_2). One class: the 1/2 split is BRCA-only and not needed pan-cancer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Tumor</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Tumor</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>AC-like; Epithelium (INOS+); Epithelium (INOS-); G1S; G2M; Invasive_Tumor; MES-like; NPC-like; OC-like; Prolif_Invasive_Tumor; T_Cell_&amp;_Tumor_Hybrid</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>BRCA; HCC; GBM</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CRC; Prostate; extra HCC</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>malignant compartment</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Invasive / cycling malignant parenchyma (BRCA invasive, HCC INOS±, GBM states). Reserved for CRC / Prostate tumor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Alveolar</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>AT1; AT2; Proliferating AT2</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Lung</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>FRI/ARI denominator</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>FRI/ARI denominator: AT1 + AT2 + proliferating AT2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Basal; Epithelial cells; Goblet; Mesothelial; Multiciliated; PNEC; Proliferating Airway; Secretory</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Lung; PDAC; GIST</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CRC (Enterocyte/Tuft/Goblet); Prostate (Luminal)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>normal / residual epithelium</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Residual / airway / mixed epithelium (PDAC, GIST, lung secretory/basal/goblet). CRC Enterocyte / Prostate Luminal map here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Injury_epithelial</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>KRT5-/KRT17+; RASC; Transitional AT2</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Lung</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>FRI numerator</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>FRI numerator: KRT5-/KRT17+, RASC, transitional AT2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Myoepithelial</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Myoepi_ACTA2+; Myoepi_KRT15+</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>BRCA</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Prostate basal</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>breast architecture</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Breast myoepithelium (WSI-visible as a layer; hard on a 16 px patch).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>T_cell</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>CD4_T</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>CD4 T cells; CD4+ T-cells; CD4+_T_Cells; Helper T cells; Tregs</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>TLS T</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Helper / CD4 T (incl. Treg). Split from CD8 because nuclear size and helper vs cytotoxic cues are weakly visible on H&amp;E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>T_cell</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>CD8_T</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>CD8 T cells; CD8+ T-cells; CD8+_T_Cells; Cytotoxic T cells</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; HCC; PDAC</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>TLS T</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Cytotoxic / CD8 T.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>T_cell</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>T_cell</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>INFg+; Lymphocyte; NK/NKT; Proliferating NK/NKT; Proliferating T-cells; T cells</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Lung; HCC; GIST; GBM</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Unspecified T / NK / GBM Lymphocyte / proliferating T / INFg+. Use when the source does not split CD4 vs CD8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>B_Plasma</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>B_cell</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>B cells; B_Cells; Proliferating B cells</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>TLS B compartment (incl. proliferating B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>B_Plasma</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Plasma</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Plasma cells</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Lung; PDAC</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>TLS-adjacent</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Clock-face plasma cells; kept because they are often H&amp;E-visible and sit in TLS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Myeloid</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>DCs; Dendritic cells; IRF7+_DCs; LAMP3+_DCs; Langerhans cells; Migratory DCs; cDCs; pDCs</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>TLS third member. All DC / pDC / Langerhans collapsed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Myeloid</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Macrophage</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Alveolar Macrophages; Interstitial Macrophages; Mac_SEPP1; Mac_Tmr; Mac_other; Macrophages; Macrophages_1; Macrophages_2; Monocytes; Proliferating Myeloid</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>TNI myeloid</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Generic macrophages + GIST monocytes. TNI myeloid = this + Macrophage_activated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Myeloid</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Macrophage_activated</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Mac_SPP1; Macrophages - IFN-activated; Macrophages M2-like; Monocytes/MDMs; SPP1+ Macrophages</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Lung; HCC; GBM</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>TNI M2 / FRI profibrotic mac</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>TNI M2 / FRI profibrotic macs: M2-like, SPP1+, IFN-activated, Monocytes/MDMs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Myeloid</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Neutrophil</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Basophils; Mast; Mast_Cells; Neutrophils</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>inflammation</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Granulocytes (neutrophil + basophil + mast). Mast granules are H&amp;E-visible but too rare to keep a head.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Fibroblast</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Adventitial FBs; Alveolar FBs; Fibroblasts; Subpleural FBs</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Lung; HCC; PDAC; GIST</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>SRI / baseline stroma</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Quiescent / tissue fibroblasts (lung alveolar/adventitial/subpleural; CODEX Fibroblasts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Myofibroblast</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Activated Fibrotic FBs; Inflammatory FBs; Myofibroblasts; Proliferating FBs</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Lung</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>ARI + FRI fibrotic stroma</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>ARI + FRI fibrotic-stromal numerator: myofibroblasts + activated/inflammatory/proliferating FBs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Unknown; Unlabeled; Other; Stroma Uncharacterized; LowQ</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>excluded</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Dropped at train time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>CAF; Collagen_fibrils; Perivascular-Like; SMCs/Pericytes; Stromal cells; Stromal_&amp;_T_Cell_Hybrid</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; GIST; GBM</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>CRC / Prostate smooth muscle; GIST tumor</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>SRI / GIST tumor</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>CAF, collagen, GIST stromal/tumor, SMC/pericyte. GIST tumor stays here (mesenchymal).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Endothelial</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Endothelial</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Endothelial</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Arteriole; Capillary; Endothelial cells; Lymphatic; Lymphatic Endothelial cells; Vascular; Venous; lowQ_vas</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>TNI endothelium</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Blood + lymphatic + GBM Vascular. TNI endothelium.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Neural</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Neural</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Neural</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Oligodendrocyte</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>GBM</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Prostate / CRC / PDAC nerve</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>glia / reserved nerve</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Oligodendrocyte; reserved Nerve for prostate / CRC / PDAC.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -17168,7 +17304,7 @@
           <t>Mesenchymal</t>
         </is>
       </c>
-      <c r="J2" s="10" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -17247,7 +17383,7 @@
           <t>Mesenchymal</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -17326,7 +17462,7 @@
           <t>Mesenchymal</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -17405,7 +17541,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -17484,7 +17620,7 @@
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -17727,7 +17863,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -17885,7 +18021,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -17964,7 +18100,7 @@
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -18045,7 +18181,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -18124,7 +18260,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -18203,7 +18339,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -18367,7 +18503,7 @@
           <t>Mesenchymal</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -18446,7 +18582,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -18608,7 +18744,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -18687,7 +18823,7 @@
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -18770,7 +18906,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -18849,7 +18985,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -19007,7 +19143,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -19090,7 +19226,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -19254,7 +19390,7 @@
           <t>Mesenchymal</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -19333,7 +19469,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -19412,7 +19548,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -19491,7 +19627,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -19570,7 +19706,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -19886,7 +20022,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -19969,7 +20105,7 @@
           <t>Mesenchymal</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -20048,7 +20184,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -20127,7 +20263,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -20206,7 +20342,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -20447,7 +20583,7 @@
           <t>Mesenchymal</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -20530,7 +20666,7 @@
           <t>Myeloid</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -20609,7 +20745,7 @@
           <t>Mesenchymal</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -20771,7 +20907,7 @@
           <t>Lymphoid</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -20850,7 +20986,7 @@
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -21395,27 +21531,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>data/Xemium/BRCA/Annotation/GSE243275_Barcode_Cell_Type_MatricesLY.xlsx</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>celltype</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>T_Cell_&amp;_Tumor_Hybrid</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Tumor–T-cell hybrid</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Epithelial</t>
         </is>
@@ -21425,37 +21561,37 @@
           <t>Epithelial</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Tumor</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Tumor_T_hybrid</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>Tumor</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>Tumor</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -21487,7 +21623,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -21554,7 +21690,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -21621,7 +21757,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -21688,7 +21824,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -21755,7 +21891,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -21822,7 +21958,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -21889,7 +22025,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -21956,7 +22092,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -21998,67 +22134,67 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>data/Xemium/BRCA/Annotation/GSE243275_Barcode_Cell_Type_MatricesLY.xlsx</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>celltype</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Stromal_&amp;_T_Cell_Hybrid</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Stromal–T-cell hybrid</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Immune</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Stromal_T_hybrid</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -22090,7 +22226,7 @@
           <t>Stromal</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -22157,7 +22293,7 @@
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -22199,130 +22335,130 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>data/Xemium/BRCA/Annotation/GSE243275_Barcode_Cell_Type_MatricesLY.xlsx</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>celltype</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Perivascular-Like</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Perivascular</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Perivascular</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>SMC_Pericyte</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>data/Xemium/BRCA/Annotation/GSE243275_Barcode_Cell_Type_MatricesLY.xlsx</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>celltype</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Unlabeled</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="9" t="n">
         <v/>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="9" t="n">
         <v/>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -22455,7 +22591,7 @@
           <t>Stromal</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -22522,7 +22658,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -22589,7 +22725,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -22656,7 +22792,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -22723,7 +22859,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -22790,7 +22926,7 @@
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -22924,7 +23060,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -22991,7 +23127,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -23058,7 +23194,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -23125,7 +23261,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -23234,126 +23370,126 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>data/CODEX/HCC/Michael_data_transfer/s4769/HE/s4769_he_mapping_updated_Visium.xlsx</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Celltype</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="9" t="n">
         <v/>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="9" t="n">
         <v/>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>data/CODEX/HCC/Michael_data_transfer/s4769/HE/s4769_he_mapping_updated_Visium.xlsx</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Celltype</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Stroma Uncharacterized</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="9" t="n">
         <v/>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="9" t="n">
         <v/>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -23569,7 +23705,7 @@
           <t>Stromal</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -23641,7 +23777,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -23713,7 +23849,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -23785,7 +23921,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -23857,7 +23993,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -23929,7 +24065,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -24001,7 +24137,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -24073,7 +24209,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -24145,7 +24281,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -24217,7 +24353,7 @@
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -24259,68 +24395,68 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>data/CODEX/HCC/Michael_data_transfer/s1167/raw_metadata_updated.xlsx</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Celltype</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Pancreas TMA</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="9" t="n">
         <v/>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="9" t="n">
         <v/>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -24536,7 +24672,7 @@
           <t>Stromal</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -24608,7 +24744,7 @@
           <t>Stromal</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
@@ -24680,7 +24816,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -24752,7 +24888,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -24824,7 +24960,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -24896,7 +25032,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -24968,7 +25104,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -25040,7 +25176,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -25112,7 +25248,7 @@
           <t>Immune</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Immune</t>
         </is>
@@ -25184,7 +25320,7 @@
           <t>Endothelial</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Endothelial</t>
         </is>
@@ -25226,68 +25362,68 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>data/CODEX/HCC/Michael_data_transfer/s1167/raw_metadata_updated.xlsx</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Celltype</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>GIST TMA</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="9" t="n">
         <v/>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="9" t="n">
         <v/>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>Stromal</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>N</t>
         </is>

--- a/code/Hist2Pheno_pkg/dataset/PanCancerCellType.xlsx
+++ b/code/Hist2Pheno_pkg/dataset/PanCancerCellType.xlsx
@@ -17,19 +17,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PDAC" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIST" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GBM" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GBM_unique_L2" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRC" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GBM_unique_L2" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'celltype'!$A$1:$J$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'celltype_fine'!$A$1:$H$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'summary'!$A$1:$Q$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'summary'!$A$1:$Q$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Lung'!$A$1:$Q$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRCA'!$A$1:$M$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'HCC'!$A$1:$M$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PDAC'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GIST'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'GBM'!$A$1:$Q$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'GBM_unique_L2'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'CRC'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'GBM_unique_L2'!$A$1:$J$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -265,7 +267,29 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_GBM_unique_L2" displayName="T_GBM_unique_L2" ref="A1:J18" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_CRC" displayName="T_CRC" ref="A1:M40" headerRowCount="1">
+  <autoFilter ref="A1:M40"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="source_file"/>
+    <tableColumn id="2" name="source_sheet"/>
+    <tableColumn id="3" name="celltype_level1"/>
+    <tableColumn id="4" name="celltype_level12"/>
+    <tableColumn id="5" name="celltype_level2"/>
+    <tableColumn id="6" name="L1"/>
+    <tableColumn id="7" name="L12"/>
+    <tableColumn id="8" name="L2"/>
+    <tableColumn id="9" name="trainable"/>
+    <tableColumn id="10" name="L1_v1"/>
+    <tableColumn id="11" name="L12_v1"/>
+    <tableColumn id="12" name="L2_v1"/>
+    <tableColumn id="13" name="trainable_v1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="T_GBM_unique_L2" displayName="T_GBM_unique_L2" ref="A1:J18" headerRowCount="1">
   <autoFilter ref="A1:J18"/>
   <tableColumns count="10">
     <tableColumn id="1" name="celltype_level2"/>
@@ -301,8 +325,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_summary" displayName="T_summary" ref="A1:Q7" headerRowCount="1">
-  <autoFilter ref="A1:Q7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_summary" displayName="T_summary" ref="A1:Q8" headerRowCount="1">
+  <autoFilter ref="A1:Q8"/>
   <tableColumns count="17">
     <tableColumn id="1" name="cancer"/>
     <tableColumn id="2" name="full_name"/>
@@ -757,7 +781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -774,7 +798,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One workbook: sheet celltype = HE-realistic training heads (5/8/20 = 17 core + 3 lung); sheet celltype_fine = v0 inventory (5/11/59). CODEX ESCC omitted.</t>
+          <t>One workbook: sheet celltype = HE-realistic training heads (5/8/20 = 17 core + 3 lung); sheet celltype_fine = v0 inventory (5/11/65). Seven public cohorts (CRC mapped onto existing v1 L2). CODEX ESCC omitted.</t>
         </is>
       </c>
     </row>
@@ -834,7 +858,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>v0 synonym inventory: 5 L1 / 11 L12 / 59 trainable L2. Too fine for a 16 px H&amp;E patch.</t>
+          <t>v0 synonym inventory: 5 L1 / 11 L12 / 65 trainable L2 (CRC fills Enterocyte / Tuft / Nerve / Smooth_muscle). Too fine for a 16 px H&amp;E patch.</t>
         </is>
       </c>
     </row>
@@ -906,7 +930,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Original multi-level table + v0 columns L1/L12/L2 + v1 columns L1_v1/L12_v1/L2_v1.</t>
+          <t>Original multi-level table + v0 columns L1/L12/L2 + v1 columns L1_v1/L12_v1/L2_v1. Includes CRC.</t>
         </is>
       </c>
     </row>
@@ -925,7 +949,7 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>How to add CRC / Prostate</t>
+          <t>How to add Prostate</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -937,24 +961,36 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Head names</t>
+          <t>CRC</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Hist2Pheno train heads: L2=fine=final_CT, L12=intermediate=final_sublineage, L1=coarse=final_lineage.</t>
+          <t>Sheet CRC: Flex / RCTD Label1 (38 L2). v1 collapses Tumor I–V → Tumor, Enterocyte/Goblet/Tuft/NE → Epithelial, enteric glia → Neural, SM/vSM/CAF/pericyte → Stromal; CD4/CD8/B/Plasma/DC/mac/neutrophil/endothelial reuse core classes. v0 fills reserved Enterocyte / Tuft / Nerve / Smooth_muscle. Labels are transferred Visium HD RCTD, not Xenium GT.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Head names</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Hist2Pheno train heads: L2=fine=final_CT, L12=intermediate=final_sublineage, L1=coarse=final_lineage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Counts</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>GT_cells_on_HE from Hist2Pheno_Datasets.xlsx (2026-09-09 snapshot). Lung GT cells = Complete_Cases only.</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>GT_cells_on_HE from Hist2Pheno_Datasets.xlsx (2026-09-15 snapshot). Lung GT cells = Complete_Cases only. CRC = P1+P2 transferred singlets on HE.</t>
         </is>
       </c>
     </row>
@@ -12179,6 +12215,2716 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>source_sheet</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>celltype_level1</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>celltype_level12</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>celltype_level2</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>trainable</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>L1_v1</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>L12_v1</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>L2_v1</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>trainable_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Tumor I</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Tumor II</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Tumor III</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Tumor IV</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Tumor V</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Tumor</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Intestinal Epithelial</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Enterocyte</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Enterocyte</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Intestinal Epithelial</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Goblet</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Goblet</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Adipocyte</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>CAF</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>CAF</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Myofibroblast</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Myofibroblast</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Myofibroblast</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Pericytes</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Perivascular</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>SMC_Pericyte</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Proliferating Fibroblast</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Myofibroblast</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Vascular Fibroblast</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Fibroblast</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Smooth Muscle</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Smooth_muscle</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Smooth Muscle</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>SM Stress Response</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Smooth_muscle</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Smooth Muscle</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Smooth Muscle</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Smooth_muscle</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Smooth Muscle</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Unknown III (SM)</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Smooth_muscle</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Smooth Muscle</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>vSM</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Smooth_muscle</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Neuronal</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Enteric Glial</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Neural</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Neural</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Nerve</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Neural</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Neural</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Neural</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Neuronal</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Neuroendocrine</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Neuronal</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Tuft</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Tuft</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Macrophage</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Macrophage</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Macrophage</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Mast</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Mast</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Neutrophil</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Neutrophil</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Neutrophil</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Neutrophil</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Proliferating Macrophages</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Proliferating_Myeloid</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Macrophage</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>cDC I</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>mRegDC</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>pDC</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>pDC</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Myeloid</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>T cells</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>CD4 T cell</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>CD4_T</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>CD4_T</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>T cells</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>CD8 T cell</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>CD8_T</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>CD8_T</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>T cells</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>NK</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Lymphoid</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>NK</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>T_cell</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>B cells</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Mature B</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>B_cell</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>B_cell</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>B cells</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Memory B</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>B_cell</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>B_cell</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>B cells</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Plasma</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>B cells</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Proliferating Immune II</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Proliferating_B</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Immune</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>B_Plasma</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>B_cell</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Lymphatic Endothelial</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Lymphatic_endothelial</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>Endothelial</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v/>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>Unlabeled</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M40"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13155,9 +15901,9 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="72" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
@@ -13281,12 +16027,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>AC-like; Epithelium (INOS+); Epithelium (INOS-); G1S; G2M; Invasive_Tumor; MES-like; NPC-like; OC-like; Prolif_Invasive_Tumor; T_Cell_&amp;_Tumor_Hybrid</t>
+          <t>AC-like; Epithelium (INOS+); Epithelium (INOS-); G1S; G2M; Invasive_Tumor; MES-like; NPC-like; OC-like; Prolif_Invasive_Tumor; T_Cell_&amp;_Tumor_Hybrid; Tumor I; Tumor II; Tumor III; Tumor IV; Tumor V</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BRCA; HCC; GBM</t>
+          <t>BRCA; HCC; GBM; CRC</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -13296,7 +16042,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>CRC; Prostate; extra HCC</t>
+          <t>Prostate; extra HCC</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -13311,7 +16057,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Invasive / cycling malignant parenchyma (BRCA invasive, HCC INOS±, GBM states). Reserved for CRC / Prostate tumor.</t>
+          <t>Invasive / cycling malignant parenchyma (BRCA invasive, HCC INOS±, GBM states, CRC Tumor I–V). Reserved for Prostate tumor.</t>
         </is>
       </c>
     </row>
@@ -13381,12 +16127,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Basal; Epithelial cells; Goblet; Mesothelial; Multiciliated; PNEC; Proliferating Airway; Secretory</t>
+          <t>Basal; Enterocyte; Epithelial cells; Goblet; Mesothelial; Multiciliated; Neuroendocrine; PNEC; Proliferating Airway; Secretory; Tuft</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Lung; PDAC; GIST</t>
+          <t>Lung; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -13396,7 +16142,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>CRC (Enterocyte/Tuft/Goblet); Prostate (Luminal)</t>
+          <t>Prostate (Luminal)</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -13411,7 +16157,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Residual / airway / mixed epithelium (PDAC, GIST, lung secretory/basal/goblet/mesothelial). CRC Enterocyte / Prostate Luminal map here.</t>
+          <t>Residual / airway / mixed epithelium (PDAC, GIST, lung secretory/basal/goblet/mesothelial). CRC Enterocyte / Tuft / Goblet / neuroendocrine map here.</t>
         </is>
       </c>
     </row>
@@ -13533,12 +16279,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>CD4 T cells; CD4+ T-cells; CD4+_T_Cells; Helper T cells; Tregs</t>
+          <t>CD4 T cell; CD4 T cells; CD4+ T-cells; CD4+_T_Cells; Helper T cells; Tregs</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -13581,12 +16327,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>CD8 T cells; CD8+ T-cells; CD8+_T_Cells; Cytotoxic T cells</t>
+          <t>CD8 T cell; CD8 T cells; CD8+ T-cells; CD8+_T_Cells; Cytotoxic T cells</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC</t>
+          <t>Lung; BRCA; HCC; PDAC; CRC</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -13629,12 +16375,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>INFg+; Lymphocyte; NK/NKT; Proliferating NK/NKT; Proliferating T-cells; T cells</t>
+          <t>INFg+; Lymphocyte; NK; NK/NKT; Proliferating NK/NKT; Proliferating T-cells; T cells</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Lung; HCC; GIST; GBM</t>
+          <t>Lung; HCC; GIST; GBM; CRC</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -13677,12 +16423,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>B cells; B_Cells; Proliferating B cells</t>
+          <t>B cells; B_Cells; Mature B; Memory B; Proliferating B cells; Proliferating Immune II</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -13730,7 +16476,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Lung; PDAC</t>
+          <t>Lung; PDAC; CRC</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -13773,12 +16519,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>DCs; Dendritic cells; IRF7+_DCs; LAMP3+_DCs; Langerhans cells; Migratory DCs; cDCs; pDCs</t>
+          <t>DCs; Dendritic cells; IRF7+_DCs; LAMP3+_DCs; Langerhans cells; Migratory DCs; cDC I; cDCs; mRegDC; pDC; pDCs</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -13821,12 +16567,12 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Alveolar Macrophages; Interstitial Macrophages; Mac_SEPP1; Mac_Tmr; Mac_other; Macrophages; Macrophages_1; Macrophages_2; Monocytes; Proliferating Myeloid</t>
+          <t>Alveolar Macrophages; Interstitial Macrophages; Mac_SEPP1; Mac_Tmr; Mac_other; Macrophages; Macrophages_1; Macrophages_2; Monocytes; Proliferating Macrophages; Proliferating Myeloid</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; GBM; CRC</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -13922,7 +16668,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -13965,12 +16711,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Adventitial FBs; Alveolar FBs; Fibroblasts; Subpleural FBs</t>
+          <t>Adventitial FBs; Alveolar FBs; Fibroblasts; Subpleural FBs; Vascular Fibroblast</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Lung; HCC; PDAC; GIST</t>
+          <t>Lung; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -14013,12 +16759,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Activated Fibrotic FBs; Inflammatory FBs; Myofibroblasts; Proliferating FBs</t>
+          <t>Activated Fibrotic FBs; Inflammatory FBs; Myofibroblasts; Proliferating FBs; Proliferating Fibroblast</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Lung</t>
+          <t>Lung; CRC</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -14039,7 +16785,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Lung-unique extra (coarse): myofibroblasts + activated/inflammatory/proliferating FBs. ARI + FRI fibrotic-stromal numerator. One class, not four FB states.</t>
+          <t>Lung extra (coarse): myofibroblasts + activated/inflammatory/proliferating FBs. Also CRC Myofibroblast / proliferating fibroblast. ARI + FRI fibrotic-stromal numerator.</t>
         </is>
       </c>
     </row>
@@ -14066,7 +16812,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; GBM; CRC</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -14109,12 +16855,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>CAF; Collagen_fibrils; Perivascular-Like; SMCs/Pericytes; Stromal cells; Stromal_&amp;_T_Cell_Hybrid</t>
+          <t>Adipocyte; CAF; Collagen_fibrils; Epithelial; Pericytes; Perivascular-Like; SM Stress Response; SMCs/Pericytes; Smooth Muscle; Stromal cells; Stromal_&amp;_T_Cell_Hybrid; Unknown III (SM); vSM</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; GIST; GBM</t>
+          <t>Lung; BRCA; GIST; GBM; CRC</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -14124,7 +16870,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>CRC / Prostate smooth muscle; GIST tumor</t>
+          <t>Prostate smooth muscle; GIST tumor</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -14139,7 +16885,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>CAF, collagen, GIST stromal/tumor, SMC/pericyte. GIST tumor stays here (mesenchymal).</t>
+          <t>CAF, collagen, GIST stromal/tumor, SMC/pericyte, CRC smooth muscle / vSM / adipocyte. GIST tumor stays here (mesenchymal).</t>
         </is>
       </c>
     </row>
@@ -14161,12 +16907,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Arteriole; Capillary; Endothelial cells; Lymphatic; Lymphatic Endothelial cells; Vascular; Venous; lowQ_vas</t>
+          <t>Arteriole; Capillary; Endothelial cells; Lymphatic; Lymphatic Endothelial; Lymphatic Endothelial cells; Vascular; Venous; lowQ_vas</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; GBM; CRC</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -14209,12 +16955,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Oligodendrocyte</t>
+          <t>Enteric Glial; Oligodendrocyte</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>GBM</t>
+          <t>GBM; CRC</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -14224,7 +16970,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Prostate / CRC / PDAC nerve</t>
+          <t>Prostate / PDAC nerve</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -14239,7 +16985,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Oligodendrocyte; reserved Nerve for prostate / CRC / PDAC.</t>
+          <t>Oligodendrocyte + CRC enteric glia. Reserved Nerve for prostate / PDAC.</t>
         </is>
       </c>
     </row>
@@ -14266,7 +17012,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
@@ -14561,17 +17307,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Invasive_Tumor</t>
+          <t>Invasive_Tumor; Tumor I; Tumor II; Tumor III; Tumor IV; Tumor V</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BRCA</t>
+          <t>BRCA; CRC</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>CRC; Prostate; extra HCC</t>
+          <t>Prostate; extra HCC</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -14581,7 +17327,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Shared malignant epithelial / glioma parenchyma (BRCA invasive; reserved for CRC / Prostate / extra HCC).</t>
+          <t>Shared malignant epithelial / glioma parenchyma (BRCA invasive, CRC Tumor I–V; leftover reserved for Prostate / extra HCC).</t>
         </is>
       </c>
     </row>
@@ -14748,36 +17494,36 @@
       <c r="H14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Enterocyte</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>CRC</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Intestinal absorptive epithelium.</t>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>CRC intestinal absorptive epithelium (Flex Enterocyte).</t>
         </is>
       </c>
     </row>
@@ -14799,12 +17545,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Epithelial cells</t>
+          <t>Epithelial cells; Neuroendocrine</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>PDAC; GIST</t>
+          <t>PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -14838,7 +17584,7 @@
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Lung</t>
+          <t>Lung; CRC</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -15170,36 +17916,36 @@
       <c r="H27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Epithelial</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Tuft</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>CRC</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>Rare intestinal chemosensory cell.</t>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>CRC chemosensory epithelial cell (Flex parent Neuronal; unified parent Epithelial).</t>
         </is>
       </c>
     </row>
@@ -15289,12 +18035,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>CD4 T cells; CD4+ T-cells; CD4+_T_Cells; Helper T cells</t>
+          <t>CD4 T cell; CD4 T cells; CD4+ T-cells; CD4+_T_Cells; Helper T cells</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -15323,12 +18069,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>CD8 T cells; CD8+ T-cells; CD8+_T_Cells; Cytotoxic T cells</t>
+          <t>CD8 T cell; CD8 T cells; CD8+ T-cells; CD8+_T_Cells; Cytotoxic T cells</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC</t>
+          <t>Lung; BRCA; HCC; PDAC; CRC</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -15493,12 +18239,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>B cells; B_Cells</t>
+          <t>B cells; B_Cells; Mature B; Memory B</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -15532,7 +18278,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Lung; PDAC</t>
+          <t>Lung; PDAC; CRC</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -15561,12 +18307,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Proliferating B cells</t>
+          <t>Proliferating B cells; Proliferating Immune II</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Lung</t>
+          <t>Lung; CRC</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -15629,12 +18375,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>DCs; Dendritic cells; IRF7+_DCs; LAMP3+_DCs; Migratory DCs; cDCs</t>
+          <t>DCs; Dendritic cells; IRF7+_DCs; LAMP3+_DCs; Migratory DCs; cDC I; cDCs; mRegDC</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -15702,7 +18448,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GBM</t>
+          <t>Lung; BRCA; HCC; PDAC; GBM; CRC</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -15804,7 +18550,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA</t>
+          <t>Lung; BRCA; CRC</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
@@ -15872,7 +18618,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Lung; HCC; PDAC; GIST</t>
+          <t>Lung; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -15901,12 +18647,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Proliferating Myeloid</t>
+          <t>Proliferating Macrophages; Proliferating Myeloid</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Lung</t>
+          <t>Lung; CRC</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
@@ -15940,7 +18686,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Lung</t>
+          <t>Lung; CRC</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
@@ -16004,7 +18750,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Lung</t>
+          <t>Lung; CRC</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr"/>
@@ -16068,7 +18814,7 @@
       <c r="D54" s="4" t="inlineStr"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>GBM</t>
+          <t>GBM; CRC</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
@@ -16131,12 +18877,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Activated Fibrotic FBs; Adventitial FBs; Alveolar FBs; Fibroblasts; Inflammatory FBs; Proliferating FBs; Subpleural FBs</t>
+          <t>Activated Fibrotic FBs; Adventitial FBs; Alveolar FBs; Fibroblasts; Inflammatory FBs; Proliferating FBs; Proliferating Fibroblast; Subpleural FBs; Vascular Fibroblast</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Lung; HCC; PDAC; GIST</t>
+          <t>Lung; HCC; PDAC; GIST; CRC</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
@@ -16170,7 +18916,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Lung</t>
+          <t>Lung; CRC</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
@@ -16204,7 +18950,7 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Lung; BRCA; HCC; PDAC; GIST; GBM</t>
+          <t>Lung; BRCA; HCC; PDAC; GIST; GBM; CRC</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr"/>
@@ -16220,36 +18966,44 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>Stromal</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Stromal</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Smooth_muscle</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr"/>
-      <c r="E59" s="10" t="inlineStr"/>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>CRC; Prostate; GIST</t>
-        </is>
-      </c>
-      <c r="G59" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>Muscularis / vascular smooth muscle if split from SMC_Pericyte.</t>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial; SM Stress Response; Smooth Muscle; Unknown III (SM); vSM</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>CRC</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Prostate; GIST</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>CRC muscularis / vSM / SM stress / Unknown III (SM). Flex cluster 'Epithelial' under Smooth Muscle maps here.</t>
         </is>
       </c>
     </row>
@@ -16271,12 +19025,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Stromal cells</t>
+          <t>Adipocyte; Stromal cells</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>BRCA; GIST</t>
+          <t>BRCA; GIST; CRC</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -16347,12 +19101,12 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Perivascular-Like; SMCs/Pericytes</t>
+          <t>Pericytes; Perivascular-Like; SMCs/Pericytes</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Lung; BRCA</t>
+          <t>Lung; BRCA; CRC</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -16446,7 +19200,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>BRCA; HCC; GIST; GBM</t>
+          <t>BRCA; HCC; GIST; GBM; CRC</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -16475,12 +19229,12 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Lymphatic; Lymphatic Endothelial cells</t>
+          <t>Lymphatic; Lymphatic Endothelial; Lymphatic Endothelial cells</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Lung; PDAC</t>
+          <t>Lung; PDAC; CRC</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -16522,36 +19276,44 @@
       <c r="H67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Neural</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Neural</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Nerve</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr"/>
-      <c r="E68" s="10" t="inlineStr"/>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>Prostate; CRC; PDAC</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>Nerve fascicles / Schwann / enteric glia on H&amp;E.</t>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Enteric Glial</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>CRC</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Prostate; PDAC</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>CRC enteric glia (Flex Enteric Glial). Reserved also for prostate / PDAC nerve.</t>
         </is>
       </c>
     </row>
@@ -16600,7 +19362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16766,7 +19528,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>8</v>
@@ -16837,7 +19599,7 @@
         <v>11</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O3" s="4" t="n">
         <v>8</v>
@@ -16908,7 +19670,7 @@
         <v>11</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O4" s="4" t="n">
         <v>8</v>
@@ -16979,7 +19741,7 @@
         <v>11</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>8</v>
@@ -17050,7 +19812,7 @@
         <v>11</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O6" s="4" t="n">
         <v>8</v>
@@ -17121,7 +19883,7 @@
         <v>11</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>8</v>
@@ -17135,8 +19897,79 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CRC</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Colorectal carcinoma</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>xenium_crc</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>data/Xemium/CRC/Annotation/CRC_Barcode_Cell_Type_Matrices.xlsx</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>celltype</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>2 labeled (P1/P2); P5 HE only</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>364539</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial / Immune / Stromal / Endothelial (Neuronal folded into Stromal)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Epithelial / Immune / Stromal / Endothelial / Neural</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Visium HD RCTD DeconvolutionLabel1 transferred onto Xenium cells (singlet only), not native Xenium GT. Drop Unlabeled. Flex L12=9 (Tumor / Intestinal Epithelial / Fibroblast / Smooth Muscle / Myeloid / T cells / B cells / Endothelial / Neuronal). P5 HE + alignment exist; annotation sheet not written yet. Oliveira et al., Nat Genet 2025.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q7"/>
+  <autoFilter ref="A1:Q8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
